--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120066137</v>
+        <v>120100879</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598058</v>
+        <v>598046</v>
       </c>
       <c r="R12" t="n">
-        <v>6681693</v>
+        <v>6681684</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1783,19 +1783,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,15 +1800,136 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120066137</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>598058</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6681693</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
           <t>Angelica Pettersson</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>Angelica Pettersson</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120065969</v>
+        <v>120066015</v>
       </c>
       <c r="B7" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,41 +1237,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R7" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,19 +1298,14 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:13</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>54 knärötter inom 3 kvm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066438</v>
+        <v>120066327</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1415,11 +1410,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>27st på cirka 5kvm</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1430,14 +1420,24 @@
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mika Schroder</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mika Schroder</t>
+        </is>
+      </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120066239</v>
+        <v>120065969</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>105009</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,37 +1450,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R9" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,11 +1507,21 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1522,14 +1532,24 @@
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120066327</v>
+        <v>120066239</v>
       </c>
       <c r="B10" t="n">
-        <v>105009</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1542,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,14 +1634,24 @@
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mika Schroder</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mika Schroder</t>
+        </is>
+      </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120067451</v>
+        <v>120066137</v>
       </c>
       <c r="B11" t="n">
-        <v>91861</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,41 +1660,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R11" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1691,21 +1729,42 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1812,61 +1871,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120066137</v>
+        <v>120067451</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>91861</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R13" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1893,40 +1944,29 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120066015</v>
+        <v>120065969</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,41 +1237,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R7" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,14 +1298,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>54 knärötter inom 3 kvm</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066327</v>
+        <v>120066282</v>
       </c>
       <c r="B8" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,25 +1349,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1434,7 +1439,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120065969</v>
+        <v>120066327</v>
       </c>
       <c r="B9" t="n">
         <v>105009</v>
@@ -1470,17 +1475,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R9" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,19 +1512,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,12 +1529,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120066137</v>
+        <v>120100879</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,49 +1655,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598058</v>
+        <v>598046</v>
       </c>
       <c r="R11" t="n">
-        <v>6681693</v>
+        <v>6681684</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,50 +1716,39 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120100879</v>
+        <v>120066137</v>
       </c>
       <c r="B12" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,41 +1757,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598046</v>
+        <v>598058</v>
       </c>
       <c r="R12" t="n">
-        <v>6681684</v>
+        <v>6681693</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,29 +1826,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120065969</v>
+        <v>120066090</v>
       </c>
       <c r="B7" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,41 +1237,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R7" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,19 +1298,14 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:13</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>52 st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1320,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066282</v>
+        <v>120066327</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120066327</v>
+        <v>120066239</v>
       </c>
       <c r="B9" t="n">
-        <v>105009</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1455,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120066239</v>
+        <v>120065969</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>105009</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,37 +1552,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R10" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1614,9 +1609,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,12 +1636,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120066090</v>
+        <v>120066551</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>52 st</t>
+          <t>Cirka 50st på 2kvm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1335,7 @@
         <v>120066327</v>
       </c>
       <c r="B8" t="n">
-        <v>105009</v>
+        <v>105032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120066239</v>
+        <v>120065969</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>105032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,37 +1450,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R9" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,9 +1507,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120065969</v>
+        <v>120066239</v>
       </c>
       <c r="B10" t="n">
-        <v>105009</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,37 +1562,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R10" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1609,19 +1619,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,22 +1636,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120100879</v>
+        <v>120066137</v>
       </c>
       <c r="B11" t="n">
-        <v>105009</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,41 +1660,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598046</v>
+        <v>598058</v>
       </c>
       <c r="R11" t="n">
-        <v>6681684</v>
+        <v>6681693</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1721,39 +1729,50 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120066137</v>
+        <v>120100879</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>105032</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,49 +1781,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598058</v>
+        <v>598046</v>
       </c>
       <c r="R12" t="n">
-        <v>6681693</v>
+        <v>6681684</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1831,40 +1842,29 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1874,7 +1874,7 @@
         <v>120067451</v>
       </c>
       <c r="B13" t="n">
-        <v>91861</v>
+        <v>91879</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -1225,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120066551</v>
+        <v>120066015</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Cirka 50st på 2kvm</t>
+          <t>54 knärötter inom 3 kvm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066327</v>
+        <v>120065969</v>
       </c>
       <c r="B8" t="n">
         <v>105032</v>
@@ -1368,17 +1368,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R8" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,9 +1405,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,19 +1432,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120065969</v>
+        <v>120066327</v>
       </c>
       <c r="B9" t="n">
         <v>105032</v>
@@ -1470,17 +1480,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R9" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,19 +1517,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,12 +1534,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120066137</v>
+        <v>120100879</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,49 +1660,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598058</v>
+        <v>598046</v>
       </c>
       <c r="R11" t="n">
-        <v>6681693</v>
+        <v>6681684</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,50 +1721,39 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120100879</v>
+        <v>120066137</v>
       </c>
       <c r="B12" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,41 +1762,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598046</v>
+        <v>598058</v>
       </c>
       <c r="R12" t="n">
-        <v>6681684</v>
+        <v>6681693</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,29 +1831,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120066015</v>
+        <v>120066239</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1301,11 +1301,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>54 knärötter inom 3 kvm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120065969</v>
+        <v>120066090</v>
       </c>
       <c r="B8" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,41 +1339,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R8" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,19 +1400,14 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:13</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>52 st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,12 +1422,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1546,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120066239</v>
+        <v>120065969</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>105032</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,37 +1552,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R10" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1619,9 +1609,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,22 +1636,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120100879</v>
+        <v>120066137</v>
       </c>
       <c r="B11" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,41 +1660,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598046</v>
+        <v>598058</v>
       </c>
       <c r="R11" t="n">
-        <v>6681684</v>
+        <v>6681693</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1721,39 +1729,50 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120066137</v>
+        <v>120100879</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,49 +1781,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598058</v>
+        <v>598046</v>
       </c>
       <c r="R12" t="n">
-        <v>6681693</v>
+        <v>6681684</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1831,40 +1842,29 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1971,6 +1971,430 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120437772</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Färmansbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>598052</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6681646</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mikael Nyman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mikael Nyman, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120437775</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105032</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Färmansbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>598046</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6681687</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mikael Nyman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mikael Nyman, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120437767</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Färmansbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>598077</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6681631</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mikael Nyman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mikael Nyman, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120437770</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Färmansbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>598053</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6681664</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mikael Nyman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mikael Nyman, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066090</v>
+        <v>120066282</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1403,11 +1403,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>52 st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1973,7 +1968,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120437772</v>
+        <v>120437767</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2008,7 +2003,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2017,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598052</v>
+        <v>598077</v>
       </c>
       <c r="R14" t="n">
-        <v>6681646</v>
+        <v>6681631</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120437775</v>
+        <v>120437772</v>
       </c>
       <c r="B15" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,30 +2086,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2123,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598046</v>
+        <v>598052</v>
       </c>
       <c r="R15" t="n">
-        <v>6681687</v>
+        <v>6681646</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120437767</v>
+        <v>120437775</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,30 +2192,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2229,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598077</v>
+        <v>598046</v>
       </c>
       <c r="R16" t="n">
-        <v>6681631</v>
+        <v>6681687</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120066239</v>
+        <v>120066282</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066282</v>
+        <v>120066239</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,25 +1339,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120066327</v>
+        <v>120065969</v>
       </c>
       <c r="B9" t="n">
         <v>105032</v>
@@ -1465,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R9" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,9 +1502,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,19 +1529,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120065969</v>
+        <v>120066327</v>
       </c>
       <c r="B10" t="n">
         <v>105032</v>
@@ -1567,17 +1577,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R10" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1604,19 +1614,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1631,12 +1631,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120437767</v>
+        <v>120437770</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2012,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598077</v>
+        <v>598053</v>
       </c>
       <c r="R14" t="n">
-        <v>6681631</v>
+        <v>6681664</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120437772</v>
+        <v>120437775</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,30 +2086,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598052</v>
+        <v>598046</v>
       </c>
       <c r="R15" t="n">
-        <v>6681646</v>
+        <v>6681687</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120437775</v>
+        <v>120437767</v>
       </c>
       <c r="B16" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,30 +2192,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598046</v>
+        <v>598077</v>
       </c>
       <c r="R16" t="n">
-        <v>6681687</v>
+        <v>6681631</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2286,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120437770</v>
+        <v>120437772</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598053</v>
+        <v>598052</v>
       </c>
       <c r="R17" t="n">
-        <v>6681664</v>
+        <v>6681646</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120066282</v>
+        <v>120065969</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,41 +1237,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R7" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,9 +1298,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066239</v>
+        <v>120066327</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
+        <v>105032</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120065969</v>
+        <v>120066438</v>
       </c>
       <c r="B9" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,41 +1451,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R9" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1502,19 +1512,14 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:13</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>27st på cirka 5kvm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120066327</v>
+        <v>120066239</v>
       </c>
       <c r="B10" t="n">
-        <v>105032</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120066137</v>
+        <v>120100879</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1655,49 +1660,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598058</v>
+        <v>598046</v>
       </c>
       <c r="R11" t="n">
-        <v>6681693</v>
+        <v>6681684</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1724,50 +1721,39 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120100879</v>
+        <v>120066137</v>
       </c>
       <c r="B12" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,41 +1762,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598046</v>
+        <v>598058</v>
       </c>
       <c r="R12" t="n">
-        <v>6681684</v>
+        <v>6681693</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1837,29 +1831,40 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1968,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120437770</v>
+        <v>120437767</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2003,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2012,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598053</v>
+        <v>598077</v>
       </c>
       <c r="R14" t="n">
-        <v>6681664</v>
+        <v>6681631</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2185,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120437767</v>
+        <v>120437770</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2215,7 +2220,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2224,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598077</v>
+        <v>598053</v>
       </c>
       <c r="R16" t="n">
-        <v>6681631</v>
+        <v>6681664</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -1225,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120065969</v>
+        <v>120066239</v>
       </c>
       <c r="B7" t="n">
-        <v>105032</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,37 +1241,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598058</v>
+        <v>598055</v>
       </c>
       <c r="R7" t="n">
-        <v>6681693</v>
+        <v>6681668</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,19 +1298,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,22 +1315,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066327</v>
+        <v>120066090</v>
       </c>
       <c r="B8" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,25 +1339,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,6 +1403,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>52 st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120066438</v>
+        <v>120065969</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,41 +1446,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598055</v>
+        <v>598058</v>
       </c>
       <c r="R9" t="n">
-        <v>6681668</v>
+        <v>6681693</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,14 +1507,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>27st på cirka 5kvm</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,22 +1534,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120066239</v>
+        <v>120066327</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>105032</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1562,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1973,7 +1973,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120437767</v>
+        <v>120437772</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598077</v>
+        <v>598052</v>
       </c>
       <c r="R14" t="n">
-        <v>6681631</v>
+        <v>6681646</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120437775</v>
+        <v>120437767</v>
       </c>
       <c r="B15" t="n">
-        <v>105032</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,30 +2091,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598046</v>
+        <v>598077</v>
       </c>
       <c r="R15" t="n">
-        <v>6681687</v>
+        <v>6681631</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120437770</v>
+        <v>120437775</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,25 +2197,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598053</v>
+        <v>598046</v>
       </c>
       <c r="R16" t="n">
-        <v>6681664</v>
+        <v>6681687</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120437772</v>
+        <v>120437770</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598052</v>
+        <v>598053</v>
       </c>
       <c r="R17" t="n">
-        <v>6681646</v>
+        <v>6681664</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116737852</v>
+        <v>120066239</v>
       </c>
       <c r="B2" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Färmansbo (Färmansbo), Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598162</v>
+        <v>598055</v>
       </c>
       <c r="R2" t="n">
-        <v>6681671</v>
+        <v>6681668</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,71 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116733495</v>
+        <v>120437777</v>
       </c>
       <c r="B3" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kuggänget (Kuggänget), Gstr</t>
+          <t>Färmansbo, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598129</v>
+        <v>598138</v>
       </c>
       <c r="R3" t="n">
-        <v>6681660</v>
+        <v>6681604</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,66 +857,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Mikael Nyman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Mikael Nyman, Beke Regelin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116732662</v>
+        <v>120067451</v>
       </c>
       <c r="B4" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Färmansbo (Färmansbo), Gstr</t>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598168</v>
+        <v>598055</v>
       </c>
       <c r="R4" t="n">
-        <v>6681616</v>
+        <v>6681668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Mika Schroder</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116736484</v>
+        <v>116732662</v>
       </c>
       <c r="B5" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,24 +996,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fagerfallet (Fagerfallet), Gstr</t>
+          <t>Färmansbo, Färmansbo, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598072</v>
+        <v>598168</v>
       </c>
       <c r="R5" t="n">
-        <v>6681652</v>
+        <v>6681616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,12 +1070,7 @@
         <v>116732993</v>
       </c>
       <c r="B6" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,7 +1107,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Färmansbo (Färmansbo), Gstr</t>
+          <t>Färmansbo, Färmansbo, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1225,50 +1173,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120066239</v>
+        <v>116733147</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Kuggänget, Kuggänget, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598055</v>
+        <v>598129</v>
       </c>
       <c r="R7" t="n">
-        <v>6681668</v>
+        <v>6681660</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,12 +1242,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,27 +1262,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120066282</v>
+        <v>116736290</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,17 +1302,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fagerfallet, Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598055</v>
+        <v>598072</v>
       </c>
       <c r="R8" t="n">
-        <v>6681668</v>
+        <v>6681652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,12 +1348,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,65 +1368,69 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120065969</v>
+        <v>116737852</v>
       </c>
       <c r="B9" t="n">
-        <v>105032</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fagerfallet, Gstr</t>
+          <t>Färmansbo, Färmansbo, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598058</v>
+        <v>598162</v>
       </c>
       <c r="R9" t="n">
-        <v>6681693</v>
+        <v>6681671</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,22 +1454,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:13</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:13</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,49 +1474,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120066327</v>
+        <v>120066015</v>
       </c>
       <c r="B10" t="n">
-        <v>105032</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1617,6 +1557,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>54 knärötter inom 3 kvm</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,53 +1588,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120100879</v>
+        <v>120066137</v>
       </c>
       <c r="B11" t="n">
-        <v>105032</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598046</v>
+        <v>598058</v>
       </c>
       <c r="R11" t="n">
-        <v>6681684</v>
+        <v>6681693</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1716,44 +1664,50 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Angelica Pettersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120066137</v>
+        <v>120100876</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,26 +1734,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>65</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598058</v>
+        <v>598081</v>
       </c>
       <c r="R12" t="n">
-        <v>6681693</v>
+        <v>6681623</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1826,19 +1776,9 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,62 +1794,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Angelica Pettersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120067451</v>
+        <v>120437767</v>
       </c>
       <c r="B13" t="n">
-        <v>91879</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fagerfallet, Fagerfallet, Gstr</t>
+          <t>Färmansbo, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598055</v>
+        <v>598077</v>
       </c>
       <c r="R13" t="n">
-        <v>6681668</v>
+        <v>6681631</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,27 +1895,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Mikael Nyman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mika Schroder</t>
+          <t>Mikael Nyman, Beke Regelin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120437770</v>
+        <v>120437769</v>
       </c>
       <c r="B14" t="n">
-        <v>98040</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598053</v>
+        <v>598129</v>
       </c>
       <c r="R14" t="n">
-        <v>6681664</v>
+        <v>6681591</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2074,15 +2008,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120437767</v>
+        <v>120437770</v>
       </c>
       <c r="B15" t="n">
-        <v>98040</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2038,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2118,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598077</v>
+        <v>598053</v>
       </c>
       <c r="R15" t="n">
-        <v>6681631</v>
+        <v>6681664</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,12 +2112,7 @@
         <v>120437772</v>
       </c>
       <c r="B16" t="n">
-        <v>98040</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2286,15 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120437775</v>
+        <v>120065969</v>
       </c>
       <c r="B17" t="n">
-        <v>105145</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,24 +2238,20 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Färmansbo, Gstr</t>
+          <t>Fagerfallet, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598046</v>
+        <v>598058</v>
       </c>
       <c r="R17" t="n">
-        <v>6681687</v>
+        <v>6681693</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2363,9 +2278,19 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,15 +2305,411 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Angelica Pettersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120066327</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Fagerfallet, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>598055</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6681668</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mika Schroder</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mika Schroder</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120100879</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Fagerfallet, Gstr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>598046</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6681684</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120437774</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Färmansbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>598137</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6681600</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Mikael Nyman</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Mikael Nyman, Beke Regelin</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120437775</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Färmansbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>598046</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6681687</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Österfärnebo</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mikael Nyman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mikael Nyman, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15650-2024 artfynd.xlsx
+++ b/artfynd/A 15650-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120066239</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437777</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120067451</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116732662</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116732993</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116733147</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116736290</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1483,6 +1523,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116737852</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120066015</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120066137</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120100876</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437767</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2005,6 +2070,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437769</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2106,6 +2176,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437770</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437772</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2314,6 +2394,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120065969</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2411,6 +2496,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120066327</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120100879</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,6 +2704,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437774</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2710,8 +2810,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120437775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>